--- a/정렬결과.xlsx
+++ b/정렬결과.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>경로</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>시간4</t>
+  </si>
+  <si>
+    <t>라벨</t>
   </si>
   <si>
     <t>시간합</t>
@@ -599,10 +602,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,10 +624,13 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>23</v>
@@ -639,12 +645,15 @@
         <v>1</v>
       </c>
       <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -659,12 +668,15 @@
         <v>5</v>
       </c>
       <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>23</v>
@@ -679,12 +691,15 @@
         <v>4</v>
       </c>
       <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>23</v>
@@ -699,12 +714,15 @@
         <v>4</v>
       </c>
       <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>23</v>
@@ -719,12 +737,15 @@
         <v>4</v>
       </c>
       <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>23</v>
@@ -739,12 +760,15 @@
         <v>1</v>
       </c>
       <c r="F7">
+        <v>28</v>
+      </c>
+      <c r="G7">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>23</v>
@@ -759,12 +783,15 @@
         <v>2</v>
       </c>
       <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>23</v>
@@ -779,12 +806,15 @@
         <v>5</v>
       </c>
       <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>20</v>
@@ -799,12 +829,15 @@
         <v>1</v>
       </c>
       <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>23</v>
@@ -819,12 +852,15 @@
         <v>2</v>
       </c>
       <c r="F11">
+        <v>26</v>
+      </c>
+      <c r="G11">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -839,12 +875,15 @@
         <v>5</v>
       </c>
       <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -859,12 +898,15 @@
         <v>2</v>
       </c>
       <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>23</v>
@@ -879,12 +921,15 @@
         <v>1</v>
       </c>
       <c r="F14">
+        <v>23</v>
+      </c>
+      <c r="G14">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>23</v>
@@ -899,12 +944,15 @@
         <v>5</v>
       </c>
       <c r="F15">
+        <v>13</v>
+      </c>
+      <c r="G15">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>23</v>
@@ -919,12 +967,15 @@
         <v>2</v>
       </c>
       <c r="F16">
+        <v>26</v>
+      </c>
+      <c r="G16">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>23</v>
@@ -939,12 +990,15 @@
         <v>5</v>
       </c>
       <c r="F17">
+        <v>32</v>
+      </c>
+      <c r="G17">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>23</v>
@@ -959,12 +1013,15 @@
         <v>5</v>
       </c>
       <c r="F18">
+        <v>16</v>
+      </c>
+      <c r="G18">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>23</v>
@@ -979,12 +1036,15 @@
         <v>5</v>
       </c>
       <c r="F19">
+        <v>23</v>
+      </c>
+      <c r="G19">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>21</v>
@@ -999,12 +1059,15 @@
         <v>5</v>
       </c>
       <c r="F20">
+        <v>36</v>
+      </c>
+      <c r="G20">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>23</v>
@@ -1019,12 +1082,15 @@
         <v>5</v>
       </c>
       <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>23</v>
@@ -1039,12 +1105,15 @@
         <v>1</v>
       </c>
       <c r="F22">
+        <v>22</v>
+      </c>
+      <c r="G22">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>23</v>
@@ -1059,12 +1128,15 @@
         <v>1</v>
       </c>
       <c r="F23">
+        <v>29</v>
+      </c>
+      <c r="G23">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1079,12 +1151,15 @@
         <v>5</v>
       </c>
       <c r="F24">
+        <v>34</v>
+      </c>
+      <c r="G24">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>20</v>
@@ -1099,12 +1174,15 @@
         <v>5</v>
       </c>
       <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <v>23</v>
@@ -1119,12 +1197,15 @@
         <v>6</v>
       </c>
       <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>23</v>
@@ -1139,73 +1220,85 @@
         <v>2</v>
       </c>
       <c r="F27">
+        <v>20</v>
+      </c>
+      <c r="G27">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28">
+        <v>23</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
+        <v>26</v>
+      </c>
+      <c r="G28">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
         <v>32</v>
       </c>
-      <c r="B28">
-        <v>23</v>
-      </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
-      <c r="F28">
+      <c r="G29">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29">
-        <v>23</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
-      <c r="F29">
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+      <c r="F30">
+        <v>35</v>
+      </c>
+      <c r="G30">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30">
-        <v>23</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>5</v>
-      </c>
-      <c r="E30">
-        <v>6</v>
-      </c>
-      <c r="F30">
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
       <c r="B31">
         <v>23</v>
       </c>
@@ -1219,12 +1312,15 @@
         <v>11</v>
       </c>
       <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>23</v>
@@ -1239,12 +1335,15 @@
         <v>7</v>
       </c>
       <c r="F32">
+        <v>10</v>
+      </c>
+      <c r="G32">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>23</v>
@@ -1259,52 +1358,61 @@
         <v>7</v>
       </c>
       <c r="F33">
+        <v>29</v>
+      </c>
+      <c r="G33">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <v>23</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>17</v>
+      </c>
+      <c r="G34">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35">
+        <v>23</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35">
+        <v>18</v>
+      </c>
+      <c r="G35">
         <v>38</v>
       </c>
-      <c r="B34">
-        <v>23</v>
-      </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34">
-        <v>5</v>
-      </c>
-      <c r="E34">
-        <v>5</v>
-      </c>
-      <c r="F34">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35">
-        <v>23</v>
-      </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35">
-        <v>5</v>
-      </c>
-      <c r="E35">
-        <v>6</v>
-      </c>
-      <c r="F35">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36">
         <v>23</v>
@@ -1319,12 +1427,15 @@
         <v>1</v>
       </c>
       <c r="F36">
+        <v>32</v>
+      </c>
+      <c r="G36">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37">
         <v>23</v>
@@ -1339,12 +1450,15 @@
         <v>7</v>
       </c>
       <c r="F37">
+        <v>20</v>
+      </c>
+      <c r="G37">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38">
         <v>23</v>
@@ -1359,12 +1473,15 @@
         <v>5</v>
       </c>
       <c r="F38">
+        <v>32</v>
+      </c>
+      <c r="G38">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39">
         <v>20</v>
@@ -1379,12 +1496,15 @@
         <v>1</v>
       </c>
       <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40">
         <v>20</v>
@@ -1399,12 +1519,15 @@
         <v>1</v>
       </c>
       <c r="F40">
+        <v>9</v>
+      </c>
+      <c r="G40">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41">
         <v>23</v>
@@ -1419,12 +1542,15 @@
         <v>2</v>
       </c>
       <c r="F41">
+        <v>36</v>
+      </c>
+      <c r="G41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42">
         <v>23</v>
@@ -1439,12 +1565,15 @@
         <v>5</v>
       </c>
       <c r="F42">
+        <v>18</v>
+      </c>
+      <c r="G42">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>20</v>
@@ -1459,12 +1588,15 @@
         <v>2</v>
       </c>
       <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>23</v>
@@ -1479,12 +1611,15 @@
         <v>11</v>
       </c>
       <c r="F44">
+        <v>33</v>
+      </c>
+      <c r="G44">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>20</v>
@@ -1499,12 +1634,15 @@
         <v>2</v>
       </c>
       <c r="F45">
+        <v>7</v>
+      </c>
+      <c r="G45">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46">
         <v>23</v>
@@ -1519,12 +1657,15 @@
         <v>11</v>
       </c>
       <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47">
         <v>23</v>
@@ -1539,12 +1680,15 @@
         <v>7</v>
       </c>
       <c r="F47">
+        <v>13</v>
+      </c>
+      <c r="G47">
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48">
         <v>23</v>
@@ -1559,12 +1703,15 @@
         <v>1</v>
       </c>
       <c r="F48">
+        <v>19</v>
+      </c>
+      <c r="G48">
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49">
         <v>23</v>
@@ -1579,12 +1726,15 @@
         <v>8</v>
       </c>
       <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49">
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50">
         <v>23</v>
@@ -1599,12 +1749,15 @@
         <v>8</v>
       </c>
       <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51">
         <v>23</v>
@@ -1619,12 +1772,15 @@
         <v>5</v>
       </c>
       <c r="F51">
+        <v>36</v>
+      </c>
+      <c r="G51">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52">
         <v>23</v>
@@ -1639,12 +1795,15 @@
         <v>2</v>
       </c>
       <c r="F52">
+        <v>17</v>
+      </c>
+      <c r="G52">
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>20</v>
@@ -1659,12 +1818,15 @@
         <v>7</v>
       </c>
       <c r="F53">
+        <v>11</v>
+      </c>
+      <c r="G53">
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54">
         <v>23</v>
@@ -1679,12 +1841,15 @@
         <v>7</v>
       </c>
       <c r="F54">
+        <v>27</v>
+      </c>
+      <c r="G54">
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B55">
         <v>23</v>
@@ -1699,12 +1864,15 @@
         <v>11</v>
       </c>
       <c r="F55">
+        <v>16</v>
+      </c>
+      <c r="G55">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B56">
         <v>20</v>
@@ -1719,12 +1887,15 @@
         <v>5</v>
       </c>
       <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57">
         <v>23</v>
@@ -1739,12 +1910,15 @@
         <v>8</v>
       </c>
       <c r="F57">
+        <v>30</v>
+      </c>
+      <c r="G57">
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B58">
         <v>20</v>
@@ -1759,12 +1933,15 @@
         <v>5</v>
       </c>
       <c r="F58">
+        <v>6</v>
+      </c>
+      <c r="G58">
         <v>44</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B59">
         <v>20</v>
@@ -1779,12 +1956,15 @@
         <v>8</v>
       </c>
       <c r="F59">
+        <v>14</v>
+      </c>
+      <c r="G59">
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B60">
         <v>20</v>
@@ -1799,12 +1979,15 @@
         <v>8</v>
       </c>
       <c r="F60">
+        <v>15</v>
+      </c>
+      <c r="G60">
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B61">
         <v>23</v>
@@ -1819,12 +2002,15 @@
         <v>8</v>
       </c>
       <c r="F61">
+        <v>31</v>
+      </c>
+      <c r="G61">
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B62">
         <v>23</v>
@@ -1839,12 +2025,15 @@
         <v>7</v>
       </c>
       <c r="F62">
+        <v>23</v>
+      </c>
+      <c r="G62">
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B63">
         <v>23</v>
@@ -1859,12 +2048,15 @@
         <v>8</v>
       </c>
       <c r="F63">
+        <v>20</v>
+      </c>
+      <c r="G63">
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B64">
         <v>23</v>
@@ -1879,12 +2071,15 @@
         <v>8</v>
       </c>
       <c r="F64">
+        <v>21</v>
+      </c>
+      <c r="G64">
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B65">
         <v>23</v>
@@ -1899,12 +2094,15 @@
         <v>5</v>
       </c>
       <c r="F65">
+        <v>16</v>
+      </c>
+      <c r="G65">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66">
         <v>23</v>
@@ -1919,12 +2117,15 @@
         <v>7</v>
       </c>
       <c r="F66">
+        <v>21</v>
+      </c>
+      <c r="G66">
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67">
         <v>23</v>
@@ -1939,12 +2140,15 @@
         <v>7</v>
       </c>
       <c r="F67">
+        <v>29</v>
+      </c>
+      <c r="G67">
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B68">
         <v>23</v>
@@ -1959,12 +2163,15 @@
         <v>8</v>
       </c>
       <c r="F68">
+        <v>26</v>
+      </c>
+      <c r="G68">
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69">
         <v>23</v>
@@ -1979,12 +2186,15 @@
         <v>8</v>
       </c>
       <c r="F69">
+        <v>24</v>
+      </c>
+      <c r="G69">
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B70">
         <v>23</v>
@@ -1999,12 +2209,15 @@
         <v>8</v>
       </c>
       <c r="F70">
+        <v>27</v>
+      </c>
+      <c r="G70">
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B71">
         <v>23</v>
@@ -2019,6 +2232,9 @@
         <v>8</v>
       </c>
       <c r="F71">
+        <v>25</v>
+      </c>
+      <c r="G71">
         <v>48</v>
       </c>
     </row>

--- a/정렬결과.xlsx
+++ b/정렬결과.xlsx
@@ -31,10 +31,10 @@
     <t>시간4</t>
   </si>
   <si>
+    <t>시간합</t>
+  </si>
+  <si>
     <t>라벨</t>
-  </si>
-  <si>
-    <t>시간합</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
@@ -645,10 +645,10 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -668,10 +668,10 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -691,10 +691,10 @@
         <v>4</v>
       </c>
       <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
         <v>3</v>
-      </c>
-      <c r="G4">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -714,10 +714,10 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -737,10 +737,10 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -760,10 +760,10 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -783,10 +783,10 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -806,10 +806,10 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G10">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -852,10 +852,10 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G11">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -875,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -898,10 +898,10 @@
         <v>2</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G13">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -921,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -944,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G15">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -967,10 +967,10 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G16">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -990,10 +990,10 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1013,10 +1013,10 @@
         <v>5</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G18">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1036,10 +1036,10 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G19">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1059,10 +1059,10 @@
         <v>5</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1082,10 +1082,10 @@
         <v>5</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1105,10 +1105,10 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1128,10 +1128,10 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G23">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1151,10 +1151,10 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G24">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1174,10 +1174,10 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G25">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1197,10 +1197,10 @@
         <v>6</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G26">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1220,10 +1220,10 @@
         <v>2</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G27">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1243,10 +1243,10 @@
         <v>5</v>
       </c>
       <c r="F28">
+        <v>36</v>
+      </c>
+      <c r="G28">
         <v>26</v>
-      </c>
-      <c r="G28">
-        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1266,10 +1266,10 @@
         <v>2</v>
       </c>
       <c r="F29">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G29">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1289,10 +1289,10 @@
         <v>6</v>
       </c>
       <c r="F30">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G30">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1312,10 +1312,10 @@
         <v>11</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G31">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1335,10 +1335,10 @@
         <v>7</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G32">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1358,10 +1358,10 @@
         <v>7</v>
       </c>
       <c r="F33">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G33">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1381,10 +1381,10 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G34">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1404,10 +1404,10 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G35">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1427,10 +1427,10 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G36">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1450,10 +1450,10 @@
         <v>7</v>
       </c>
       <c r="F37">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1473,10 +1473,10 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G38">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1496,10 +1496,10 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G39">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1519,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="G40">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1542,10 +1542,10 @@
         <v>2</v>
       </c>
       <c r="F41">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G41">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1565,10 +1565,10 @@
         <v>5</v>
       </c>
       <c r="F42">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G42">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1588,10 +1588,10 @@
         <v>2</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G43">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1611,10 +1611,10 @@
         <v>11</v>
       </c>
       <c r="F44">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G44">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1634,10 +1634,10 @@
         <v>2</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G45">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1657,10 +1657,10 @@
         <v>11</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G46">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1680,10 +1680,10 @@
         <v>7</v>
       </c>
       <c r="F47">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G47">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1703,10 +1703,10 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G48">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1726,10 +1726,10 @@
         <v>8</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G49">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1749,10 +1749,10 @@
         <v>8</v>
       </c>
       <c r="F50">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G50">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1772,10 +1772,10 @@
         <v>5</v>
       </c>
       <c r="F51">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G51">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1795,10 +1795,10 @@
         <v>2</v>
       </c>
       <c r="F52">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G52">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1818,10 +1818,10 @@
         <v>7</v>
       </c>
       <c r="F53">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="G53">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1841,10 +1841,10 @@
         <v>7</v>
       </c>
       <c r="F54">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G54">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1864,10 +1864,10 @@
         <v>11</v>
       </c>
       <c r="F55">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G55">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1887,10 +1887,10 @@
         <v>5</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G56">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1910,10 +1910,10 @@
         <v>8</v>
       </c>
       <c r="F57">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G57">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1933,10 +1933,10 @@
         <v>5</v>
       </c>
       <c r="F58">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="G58">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1956,10 +1956,10 @@
         <v>8</v>
       </c>
       <c r="F59">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G59">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1979,10 +1979,10 @@
         <v>8</v>
       </c>
       <c r="F60">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="G60">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2002,10 +2002,10 @@
         <v>8</v>
       </c>
       <c r="F61">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G61">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2025,10 +2025,10 @@
         <v>7</v>
       </c>
       <c r="F62">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G62">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2048,10 +2048,10 @@
         <v>8</v>
       </c>
       <c r="F63">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G63">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2071,10 +2071,10 @@
         <v>8</v>
       </c>
       <c r="F64">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G64">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="F65">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G65">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2117,10 +2117,10 @@
         <v>7</v>
       </c>
       <c r="F66">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G66">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2140,10 +2140,10 @@
         <v>7</v>
       </c>
       <c r="F67">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G67">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2163,10 +2163,10 @@
         <v>8</v>
       </c>
       <c r="F68">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G68">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2186,10 +2186,10 @@
         <v>8</v>
       </c>
       <c r="F69">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G69">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2209,10 +2209,10 @@
         <v>8</v>
       </c>
       <c r="F70">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G70">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2232,10 +2232,10 @@
         <v>8</v>
       </c>
       <c r="F71">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G71">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/정렬결과.xlsx
+++ b/정렬결과.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>경로</t>
   </si>
@@ -37,57 +37,60 @@
     <t>라벨</t>
   </si>
   <si>
+    <t>라벨별_평균시간</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
+    <t>('엘지디스플레이 파주공장', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
@@ -97,39 +100,39 @@
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '탄현마을부영3단지아파트')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트')</t>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '일산에듀포레푸르지오아파트')</t>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산에듀포레푸르지오아파트')</t>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
@@ -145,34 +148,37 @@
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '리드인 독서논술 일산')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
@@ -181,24 +187,30 @@
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
@@ -208,43 +220,34 @@
     <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
     <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
   </si>
   <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
+  </si>
+  <si>
     <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
   </si>
 </sst>
 </file>
@@ -602,10 +605,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,10 +630,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>23</v>
@@ -650,10 +656,13 @@
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -673,10 +682,13 @@
       <c r="G3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>23</v>
@@ -696,10 +708,13 @@
       <c r="G4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>23</v>
@@ -719,10 +734,13 @@
       <c r="G5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>23</v>
@@ -742,22 +760,25 @@
       <c r="G6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>23</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -765,22 +786,25 @@
       <c r="G7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>23</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -788,22 +812,25 @@
       <c r="G8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>31</v>
@@ -811,22 +838,25 @@
       <c r="G9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>31</v>
@@ -834,22 +864,25 @@
       <c r="G10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>31</v>
@@ -857,22 +890,25 @@
       <c r="G11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>31</v>
@@ -880,10 +916,13 @@
       <c r="G12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -903,10 +942,13 @@
       <c r="G13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>23</v>
@@ -926,19 +968,22 @@
       <c r="G14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>23</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -949,10 +994,13 @@
       <c r="G15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>23</v>
@@ -972,10 +1020,13 @@
       <c r="G16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>23</v>
@@ -995,19 +1046,22 @@
       <c r="G17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>23</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -1018,10 +1072,13 @@
       <c r="G18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>23</v>
@@ -1041,10 +1098,13 @@
       <c r="G19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>21</v>
@@ -1062,12 +1122,15 @@
         <v>35</v>
       </c>
       <c r="G20">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>9</v>
+      </c>
+      <c r="H20">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>23</v>
@@ -1087,22 +1150,25 @@
       <c r="G21">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>23</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>35</v>
@@ -1110,10 +1176,13 @@
       <c r="G22">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>23</v>
@@ -1133,22 +1202,25 @@
       <c r="G23">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>23</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>35</v>
@@ -1156,22 +1228,25 @@
       <c r="G24">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>36</v>
@@ -1179,22 +1254,25 @@
       <c r="G25">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>23</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>36</v>
@@ -1202,22 +1280,25 @@
       <c r="G26">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
         <v>6</v>
       </c>
-      <c r="D27">
-        <v>5</v>
-      </c>
       <c r="E27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>36</v>
@@ -1225,22 +1306,25 @@
       <c r="G27">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>23</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28">
         <v>36</v>
@@ -1248,10 +1332,13 @@
       <c r="G28">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>23</v>
@@ -1271,22 +1358,25 @@
       <c r="G29">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>23</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>36</v>
@@ -1294,10 +1384,13 @@
       <c r="G30">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31">
         <v>23</v>
@@ -1306,21 +1399,24 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>37</v>
       </c>
       <c r="G31">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H31">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32">
         <v>23</v>
@@ -1329,21 +1425,24 @@
         <v>1</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F32">
         <v>37</v>
       </c>
       <c r="G32">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33">
         <v>23</v>
@@ -1363,10 +1462,13 @@
       <c r="G33">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34">
         <v>23</v>
@@ -1386,10 +1488,13 @@
       <c r="G34">
         <v>31</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>23</v>
@@ -1409,10 +1514,13 @@
       <c r="G35">
         <v>32</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>23</v>
@@ -1432,10 +1540,13 @@
       <c r="G36">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37">
         <v>23</v>
@@ -1455,10 +1566,13 @@
       <c r="G37">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38">
         <v>23</v>
@@ -1478,33 +1592,39 @@
       <c r="G38">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C39">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>8</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
         <v>40</v>
       </c>
       <c r="G39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>26</v>
+      </c>
+      <c r="H39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40">
         <v>20</v>
@@ -1524,56 +1644,65 @@
       <c r="G40">
         <v>29</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41">
         <v>23</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41">
         <v>40</v>
       </c>
       <c r="G41">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>40</v>
       </c>
       <c r="G42">
+        <v>5</v>
+      </c>
+      <c r="H42">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>20</v>
@@ -1591,21 +1720,24 @@
         <v>41</v>
       </c>
       <c r="G43">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>3</v>
+      </c>
+      <c r="H43">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44">
         <v>23</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44">
         <v>11</v>
@@ -1614,127 +1746,145 @@
         <v>41</v>
       </c>
       <c r="G44">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C45">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F45">
         <v>41</v>
       </c>
       <c r="G45">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>8</v>
+      </c>
+      <c r="H45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>41</v>
       </c>
       <c r="G46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>23</v>
+      </c>
+      <c r="H46">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47">
         <v>23</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F47">
         <v>41</v>
       </c>
       <c r="G47">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>17</v>
+      </c>
+      <c r="H47">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48">
         <v>23</v>
       </c>
       <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
         <v>10</v>
       </c>
-      <c r="D48">
-        <v>8</v>
-      </c>
       <c r="E48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F48">
         <v>42</v>
       </c>
       <c r="G48">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>12</v>
+      </c>
+      <c r="H48">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49">
         <v>23</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F49">
         <v>42</v>
       </c>
       <c r="G49">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="H49">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50">
         <v>23</v>
@@ -1752,87 +1902,99 @@
         <v>42</v>
       </c>
       <c r="G50">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>25</v>
+      </c>
+      <c r="H50">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51">
         <v>23</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>43</v>
       </c>
       <c r="G51">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>32</v>
+      </c>
+      <c r="H51">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52">
         <v>23</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F52">
         <v>43</v>
       </c>
       <c r="G52">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>22</v>
+      </c>
+      <c r="H52">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>43</v>
       </c>
       <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="H53">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>11</v>
@@ -1844,12 +2006,15 @@
         <v>43</v>
       </c>
       <c r="G54">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55">
         <v>23</v>
@@ -1867,41 +2032,47 @@
         <v>43</v>
       </c>
       <c r="G55">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="H55">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F56">
         <v>44</v>
       </c>
       <c r="G56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="H56">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>11</v>
@@ -1913,64 +2084,73 @@
         <v>44</v>
       </c>
       <c r="G57">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="H57">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58">
         <v>20</v>
       </c>
       <c r="C58">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F58">
         <v>44</v>
       </c>
       <c r="G58">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>6</v>
+      </c>
+      <c r="H58">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59">
         <v>20</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D59">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E59">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F59">
         <v>44</v>
       </c>
       <c r="G59">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <v>11</v>
@@ -1982,35 +2162,41 @@
         <v>44</v>
       </c>
       <c r="G60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="H60">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D61">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F61">
         <v>44</v>
       </c>
       <c r="G61">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="H61">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62">
         <v>23</v>
@@ -2028,35 +2214,41 @@
         <v>45</v>
       </c>
       <c r="G62">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="H62">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63">
         <v>23</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F63">
         <v>46</v>
       </c>
       <c r="G63">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H63">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64">
         <v>23</v>
@@ -2074,35 +2266,41 @@
         <v>46</v>
       </c>
       <c r="G64">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>34</v>
+      </c>
+      <c r="H64">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65">
         <v>23</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F65">
         <v>46</v>
       </c>
       <c r="G65">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="H65">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66">
         <v>23</v>
@@ -2122,10 +2320,13 @@
       <c r="G66">
         <v>13</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67">
         <v>23</v>
@@ -2143,12 +2344,15 @@
         <v>47</v>
       </c>
       <c r="G67">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="H67">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B68">
         <v>23</v>
@@ -2166,12 +2370,15 @@
         <v>48</v>
       </c>
       <c r="G68">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H68">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B69">
         <v>23</v>
@@ -2189,12 +2396,15 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>15</v>
+      </c>
+      <c r="H69">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B70">
         <v>23</v>
@@ -2212,12 +2422,15 @@
         <v>48</v>
       </c>
       <c r="G70">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>11</v>
+      </c>
+      <c r="H70">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71">
         <v>23</v>
@@ -2235,7 +2448,10 @@
         <v>48</v>
       </c>
       <c r="G71">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="H71">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/정렬결과.xlsx
+++ b/정렬결과.xlsx
@@ -40,214 +40,214 @@
     <t>라벨별_평균시간</t>
   </si>
   <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '광성교회', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '광성교회', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '광성교회', '리드인 독서논술 일산')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '탄현마을부영3단지아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', 'SK엔크린 삼정셀프주유소')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '대윤프라자', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', '일산에듀포레푸르지오아파트')</t>
-  </si>
-  <si>
-    <t>('엘지디스플레이 파주공장', '일산동양아파트101동', '광성교회', '리드인 독서논술 일산', '탄현마을부영3단지아파트')</t>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현큰마을대림아파트 일현로 140', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '광성교회')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '광성교회')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '광성교회')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '광성교회', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '광성교회', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '광성교회', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '광성교회', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '광성교회', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '광성교회', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '광성교회', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '광성교회')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '리드인 독서논술 일산', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현큰마을대림아파트 일현로 140', '광성교회', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '광성교회', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '광성교회', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '광성교회', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '리드인 독서논술 일산', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '광성교회', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '광성교회', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '리드인 독서논술 일산', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '일산에듀포레푸르지오아파트', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현마을부영3단지아파트', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '광성교회', '리드인 독서논술 일산', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산동양아파트101동', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '광성교회', '리드인 독서논술 일산')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '일산에듀포레푸르지오아파트', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '광성교회', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '광성교회', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '광성교회', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '일산동양아파트101동')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '탄현큰마을대림아파트 일현로 140', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현마을부영3단지아파트', '광성교회', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '일산에듀포레푸르지오아파트', '광성교회', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', 'SK엔크린 삼정셀프주유소', '광성교회', '리드인 독서논술 일산', '대윤프라자')</t>
+  </si>
+  <si>
+    <t>('엘지디스플레이 파주공장', '탄현큰마을대림아파트 일현로 140', '광성교회', '리드인 독서논술 일산', '대윤프라자')</t>
   </si>
 </sst>
 </file>
@@ -639,25 +639,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -665,25 +665,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>35.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -691,25 +691,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>35.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -717,25 +717,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -743,25 +743,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -769,7 +769,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -781,13 +781,13 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>6</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -795,7 +795,7 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -804,16 +804,16 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>7</v>
       </c>
       <c r="H8">
-        <v>38.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -821,25 +821,25 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -847,25 +847,25 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>9</v>
       </c>
       <c r="H10">
-        <v>33</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -873,25 +873,25 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>5</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G11">
         <v>10</v>
       </c>
       <c r="H11">
-        <v>34</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -899,25 +899,25 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G12">
         <v>11</v>
       </c>
       <c r="H12">
-        <v>39.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -925,25 +925,25 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G13">
         <v>12</v>
       </c>
       <c r="H13">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -951,7 +951,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G14">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>39.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -977,25 +977,25 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G15">
         <v>14</v>
       </c>
       <c r="H15">
-        <v>38.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1003,25 +1003,25 @@
         <v>22</v>
       </c>
       <c r="B16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G16">
         <v>15</v>
       </c>
       <c r="H16">
-        <v>40.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1029,25 +1029,25 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G17">
         <v>16</v>
       </c>
       <c r="H17">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1055,25 +1055,25 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G18">
         <v>17</v>
       </c>
       <c r="H18">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1081,25 +1081,25 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
         <v>2</v>
       </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <v>5</v>
-      </c>
       <c r="F19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19">
         <v>18</v>
       </c>
       <c r="H19">
-        <v>41</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1107,25 +1107,25 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1133,25 +1133,25 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21">
-        <v>39.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1159,7 +1159,7 @@
         <v>28</v>
       </c>
       <c r="B22">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -1168,16 +1168,16 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22">
+        <v>30</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+      <c r="H22">
         <v>35</v>
-      </c>
-      <c r="G22">
-        <v>20</v>
-      </c>
-      <c r="H22">
-        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1185,25 +1185,25 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23">
-        <v>40</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1211,25 +1211,25 @@
         <v>30</v>
       </c>
       <c r="B24">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24">
+        <v>31</v>
+      </c>
+      <c r="G24">
         <v>23</v>
       </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
-      <c r="D24">
-        <v>5</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>35</v>
-      </c>
-      <c r="G24">
-        <v>22</v>
-      </c>
-      <c r="H24">
-        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1237,7 +1237,7 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1249,13 +1249,13 @@
         <v>6</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25">
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1263,25 +1263,25 @@
         <v>32</v>
       </c>
       <c r="B26">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26">
-        <v>42</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1289,25 +1289,25 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H27">
-        <v>39</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1315,25 +1315,25 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H28">
-        <v>38</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1341,25 +1341,25 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G29">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H29">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1367,25 +1367,25 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G30">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H30">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1393,25 +1393,25 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H31">
-        <v>38.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1419,25 +1419,25 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F32">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H32">
-        <v>34</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1445,25 +1445,25 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G33">
         <v>30</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1471,7 +1471,7 @@
         <v>40</v>
       </c>
       <c r="B34">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C34">
         <v>4</v>
@@ -1480,16 +1480,16 @@
         <v>5</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G34">
         <v>31</v>
       </c>
       <c r="H34">
-        <v>41.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1497,7 +1497,7 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1509,13 +1509,13 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G35">
         <v>32</v>
       </c>
       <c r="H35">
-        <v>40.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1523,25 +1523,25 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G36">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1549,25 +1549,25 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>7</v>
       </c>
       <c r="F37">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G37">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H37">
-        <v>40.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1575,25 +1575,25 @@
         <v>44</v>
       </c>
       <c r="B38">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G38">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H38">
-        <v>43</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1601,25 +1601,25 @@
         <v>45</v>
       </c>
       <c r="B39">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>8</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G39">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1627,22 +1627,22 @@
         <v>46</v>
       </c>
       <c r="B40">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G40">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H40">
         <v>38.5</v>
@@ -1653,25 +1653,25 @@
         <v>47</v>
       </c>
       <c r="B41">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G41">
         <v>35</v>
       </c>
       <c r="H41">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1679,25 +1679,25 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F42">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H42">
-        <v>35</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1705,25 +1705,25 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H43">
-        <v>35.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1731,25 +1731,25 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="F44">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H44">
-        <v>35.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1757,25 +1757,25 @@
         <v>51</v>
       </c>
       <c r="B45">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F45">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G45">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H45">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1783,25 +1783,25 @@
         <v>52</v>
       </c>
       <c r="B46">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C46">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>11</v>
+      </c>
+      <c r="F46">
+        <v>36</v>
+      </c>
+      <c r="G46">
         <v>8</v>
       </c>
-      <c r="E46">
-        <v>2</v>
-      </c>
-      <c r="F46">
-        <v>41</v>
-      </c>
-      <c r="G46">
-        <v>23</v>
-      </c>
       <c r="H46">
-        <v>38.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1809,25 +1809,25 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47">
         <v>11</v>
       </c>
       <c r="F47">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G47">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H47">
-        <v>37</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1835,25 +1835,25 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F48">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G48">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H48">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1861,25 +1861,25 @@
         <v>55</v>
       </c>
       <c r="B49">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>8</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F49">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G49">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H49">
-        <v>40.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1887,25 +1887,25 @@
         <v>56</v>
       </c>
       <c r="B50">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F50">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G50">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>39</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1913,25 +1913,25 @@
         <v>57</v>
       </c>
       <c r="B51">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F51">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G51">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51">
-        <v>40.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1939,25 +1939,25 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E52">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F52">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G52">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H52">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1965,25 +1965,25 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F53">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G53">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H53">
-        <v>39</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1994,22 +1994,22 @@
         <v>20</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D54">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E54">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>36</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2017,25 +2017,25 @@
         <v>61</v>
       </c>
       <c r="B55">
+        <v>17</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55">
+        <v>11</v>
+      </c>
+      <c r="E55">
+        <v>7</v>
+      </c>
+      <c r="F55">
+        <v>39</v>
+      </c>
+      <c r="G55">
         <v>23</v>
       </c>
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55">
-        <v>5</v>
-      </c>
-      <c r="E55">
-        <v>11</v>
-      </c>
-      <c r="F55">
-        <v>43</v>
-      </c>
-      <c r="G55">
-        <v>16</v>
-      </c>
       <c r="H55">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2043,25 +2043,25 @@
         <v>62</v>
       </c>
       <c r="B56">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D56">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E56">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G56">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H56">
-        <v>40</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2069,25 +2069,25 @@
         <v>63</v>
       </c>
       <c r="B57">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C57">
         <v>5</v>
       </c>
       <c r="D57">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E57">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G57">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57">
-        <v>38.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2095,22 +2095,22 @@
         <v>64</v>
       </c>
       <c r="B58">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <v>11</v>
       </c>
       <c r="E58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F58">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H58">
         <v>37</v>
@@ -2121,25 +2121,25 @@
         <v>65</v>
       </c>
       <c r="B59">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C59">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>8</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F59">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H59">
-        <v>37</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2147,25 +2147,25 @@
         <v>66</v>
       </c>
       <c r="B60">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D60">
         <v>11</v>
       </c>
       <c r="E60">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F60">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G60">
+        <v>21</v>
+      </c>
+      <c r="H60">
         <v>35</v>
-      </c>
-      <c r="H60">
-        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2173,25 +2173,25 @@
         <v>67</v>
       </c>
       <c r="B61">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C61">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D61">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F61">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G61">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H61">
-        <v>39.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2199,10 +2199,10 @@
         <v>68</v>
       </c>
       <c r="B62">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <v>11</v>
@@ -2211,13 +2211,13 @@
         <v>7</v>
       </c>
       <c r="F62">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G62">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H62">
-        <v>40</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2225,25 +2225,25 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63">
+        <v>11</v>
+      </c>
+      <c r="E63">
         <v>10</v>
       </c>
-      <c r="D63">
-        <v>8</v>
-      </c>
-      <c r="E63">
-        <v>5</v>
-      </c>
       <c r="F63">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G63">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H63">
-        <v>41.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2251,25 +2251,25 @@
         <v>70</v>
       </c>
       <c r="B64">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>11</v>
       </c>
       <c r="E64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G64">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H64">
-        <v>43</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2277,25 +2277,25 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>11</v>
       </c>
       <c r="E65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F65">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G65">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>41</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2303,25 +2303,25 @@
         <v>72</v>
       </c>
       <c r="B66">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D66">
         <v>11</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F66">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G66">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H66">
-        <v>39.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2329,22 +2329,22 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D67">
         <v>11</v>
       </c>
       <c r="E67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F67">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G67">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H67">
         <v>38.5</v>
@@ -2355,25 +2355,25 @@
         <v>74</v>
       </c>
       <c r="B68">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>11</v>
       </c>
       <c r="E68">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F68">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G68">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H68">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2381,7 +2381,7 @@
         <v>75</v>
       </c>
       <c r="B69">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C69">
         <v>6</v>
@@ -2390,16 +2390,16 @@
         <v>11</v>
       </c>
       <c r="E69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F69">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G69">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H69">
-        <v>40.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2407,25 +2407,25 @@
         <v>76</v>
       </c>
       <c r="B70">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>11</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F70">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G70">
         <v>11</v>
       </c>
       <c r="H70">
-        <v>39.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2433,25 +2433,25 @@
         <v>77</v>
       </c>
       <c r="B71">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71">
         <v>11</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F71">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G71">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H71">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
